--- a/工作簿1.xlsx
+++ b/工作簿1.xlsx
@@ -4,10 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25680" windowHeight="12560"/>
+    <workbookView windowWidth="25680" windowHeight="12560" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,9 +29,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="60">
-  <si>
-    <t>玩法</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="172">
+  <si>
+    <t>张数</t>
+  </si>
+  <si>
+    <t>玩法名</t>
   </si>
   <si>
     <t>牌池</t>
@@ -47,88 +52,151 @@
     <t>额外规则</t>
   </si>
   <si>
+    <t>投注</t>
+  </si>
+  <si>
     <t>限制</t>
   </si>
   <si>
+    <t>超级3张</t>
+  </si>
+  <si>
+    <t>全部牌池</t>
+  </si>
+  <si>
     <t>3张</t>
   </si>
   <si>
-    <t>基础牌池</t>
+    <t>顺子n手</t>
+  </si>
+  <si>
+    <t>3张成顺、成花</t>
+  </si>
+  <si>
+    <t>只玩3张</t>
+  </si>
+  <si>
+    <t>同花n手</t>
+  </si>
+  <si>
+    <t>超级4张</t>
+  </si>
+  <si>
+    <t>4张</t>
+  </si>
+  <si>
+    <t>4张成顺、成花</t>
+  </si>
+  <si>
+    <t>只玩4张</t>
+  </si>
+  <si>
+    <t>joker++</t>
+  </si>
+  <si>
+    <t>joker几率0.08</t>
+  </si>
+  <si>
+    <t>5张</t>
+  </si>
+  <si>
+    <t>3条n手</t>
+  </si>
+  <si>
+    <t>葫芦n手</t>
+  </si>
+  <si>
+    <t>4条n手</t>
+  </si>
+  <si>
+    <t>4张成顺</t>
+  </si>
+  <si>
+    <t>4张成花</t>
+  </si>
+  <si>
+    <t>红色同花</t>
+  </si>
+  <si>
+    <t>♥️♦️成花</t>
+  </si>
+  <si>
+    <t>黑色同花</t>
+  </si>
+  <si>
+    <t>♠️♣️成花</t>
+  </si>
+  <si>
+    <t>单数成顺</t>
+  </si>
+  <si>
+    <t>单数顺子n手</t>
+  </si>
+  <si>
+    <t>双数成顺</t>
+  </si>
+  <si>
+    <t>双数顺子n手</t>
+  </si>
+  <si>
+    <t>超级两对</t>
+  </si>
+  <si>
+    <t>两对n手</t>
+  </si>
+  <si>
+    <t>两对赔率+1</t>
+  </si>
+  <si>
+    <t>超级三条</t>
+  </si>
+  <si>
+    <t>三条n手</t>
+  </si>
+  <si>
+    <t>三条赔率+1</t>
+  </si>
+  <si>
+    <t>超级顺子</t>
+  </si>
+  <si>
+    <t>顺子赔率+1</t>
+  </si>
+  <si>
+    <t>超级同花</t>
+  </si>
+  <si>
+    <t>同花赔率+1</t>
+  </si>
+  <si>
+    <t>超级葫芦</t>
+  </si>
+  <si>
+    <t>葫芦赔率+1</t>
+  </si>
+  <si>
+    <t>我爱一对</t>
+  </si>
+  <si>
+    <t>一对n手</t>
   </si>
   <si>
     <t>无</t>
   </si>
   <si>
-    <t>顺子n手</t>
-  </si>
-  <si>
-    <t>3张成顺、成花</t>
-  </si>
-  <si>
-    <t>可增加joker变化</t>
-  </si>
-  <si>
-    <t>只玩3张</t>
-  </si>
-  <si>
-    <t>同花n手</t>
-  </si>
-  <si>
-    <t>4张</t>
-  </si>
-  <si>
-    <t>4张成顺、成花</t>
-  </si>
-  <si>
-    <t>只玩4张</t>
-  </si>
-  <si>
-    <t>joker牌</t>
-  </si>
-  <si>
-    <t>有</t>
-  </si>
-  <si>
-    <t>5张</t>
-  </si>
-  <si>
-    <t>3条n手</t>
-  </si>
-  <si>
-    <t>最小牌型为2对</t>
-  </si>
-  <si>
-    <t>Joker几率10%</t>
-  </si>
-  <si>
-    <t>葫芦n手</t>
-  </si>
-  <si>
-    <t>4条n手</t>
-  </si>
-  <si>
-    <t>4张成顺</t>
-  </si>
-  <si>
-    <t>4张成花</t>
-  </si>
-  <si>
-    <t>♥️♦️成花</t>
-  </si>
-  <si>
-    <t>♠️♣️成花</t>
-  </si>
-  <si>
-    <t>单数成顺</t>
-  </si>
-  <si>
-    <t>单数顺子n手</t>
-  </si>
-  <si>
-    <t>双数成顺</t>
-  </si>
-  <si>
-    <t>双数顺子n手</t>
+    <t>我爱两对</t>
+  </si>
+  <si>
+    <t>我爱三条</t>
+  </si>
+  <si>
+    <t>我爱顺子</t>
+  </si>
+  <si>
+    <t>我爱同花</t>
+  </si>
+  <si>
+    <t>我爱葫芦</t>
   </si>
   <si>
     <t>不hold牌</t>
@@ -167,15 +235,9 @@
     <t>两对加成</t>
   </si>
   <si>
-    <t>两对n手</t>
-  </si>
-  <si>
     <t>三条加成</t>
   </si>
   <si>
-    <t>三条n手</t>
-  </si>
-  <si>
     <t>没有人头牌</t>
   </si>
   <si>
@@ -207,6 +269,282 @@
   </si>
   <si>
     <t>7张</t>
+  </si>
+  <si>
+    <t>Joker几率</t>
+  </si>
+  <si>
+    <t>需显示</t>
+  </si>
+  <si>
+    <t>♠️A</t>
+  </si>
+  <si>
+    <t>♠️2</t>
+  </si>
+  <si>
+    <t>♠️3</t>
+  </si>
+  <si>
+    <t>一对3手</t>
+  </si>
+  <si>
+    <t>♠️4</t>
+  </si>
+  <si>
+    <t>一对5手</t>
+  </si>
+  <si>
+    <t>♠️5</t>
+  </si>
+  <si>
+    <t>两对3手</t>
+  </si>
+  <si>
+    <t>♠️6</t>
+  </si>
+  <si>
+    <t>三条2手</t>
+  </si>
+  <si>
+    <t>♠️7</t>
+  </si>
+  <si>
+    <t>两对5手</t>
+  </si>
+  <si>
+    <t>♠️8</t>
+  </si>
+  <si>
+    <t>两对8手</t>
+  </si>
+  <si>
+    <t>♠️9</t>
+  </si>
+  <si>
+    <t>顺子2手</t>
+  </si>
+  <si>
+    <t>♠️10</t>
+  </si>
+  <si>
+    <t>♠️J</t>
+  </si>
+  <si>
+    <t>顺子3手</t>
+  </si>
+  <si>
+    <t>♠️Q</t>
+  </si>
+  <si>
+    <t>同花3手</t>
+  </si>
+  <si>
+    <t>♠️K</t>
+  </si>
+  <si>
+    <t>两对20手</t>
+  </si>
+  <si>
+    <t>♥️A</t>
+  </si>
+  <si>
+    <t>♥️2</t>
+  </si>
+  <si>
+    <t>三条5手</t>
+  </si>
+  <si>
+    <t>♥️3</t>
+  </si>
+  <si>
+    <t>双数顺子2手</t>
+  </si>
+  <si>
+    <t>♥️4</t>
+  </si>
+  <si>
+    <t>葫芦3手</t>
+  </si>
+  <si>
+    <t>♥️5</t>
+  </si>
+  <si>
+    <t>3条10手</t>
+  </si>
+  <si>
+    <t>♥️6</t>
+  </si>
+  <si>
+    <t>同花5手</t>
+  </si>
+  <si>
+    <t>♥️7</t>
+  </si>
+  <si>
+    <t>♥️8</t>
+  </si>
+  <si>
+    <t>单数顺子3手</t>
+  </si>
+  <si>
+    <t>♥️9</t>
+  </si>
+  <si>
+    <t>葫芦5手</t>
+  </si>
+  <si>
+    <t>♥️10</t>
+  </si>
+  <si>
+    <t>♥️J</t>
+  </si>
+  <si>
+    <t>♥️Q</t>
+  </si>
+  <si>
+    <t>♥️K</t>
+  </si>
+  <si>
+    <t>我爱四条</t>
+  </si>
+  <si>
+    <t>四条3手</t>
+  </si>
+  <si>
+    <t>♣️A</t>
+  </si>
+  <si>
+    <t>♣️2</t>
+  </si>
+  <si>
+    <t>♣️3</t>
+  </si>
+  <si>
+    <t>葫芦8手</t>
+  </si>
+  <si>
+    <t>♣️4</t>
+  </si>
+  <si>
+    <t>♣️5</t>
+  </si>
+  <si>
+    <t>♣️6</t>
+  </si>
+  <si>
+    <t>♣️7</t>
+  </si>
+  <si>
+    <t>三条15手</t>
+  </si>
+  <si>
+    <t>♣️8</t>
+  </si>
+  <si>
+    <t>顺子5手</t>
+  </si>
+  <si>
+    <t>♣️9</t>
+  </si>
+  <si>
+    <t>♣️10</t>
+  </si>
+  <si>
+    <t>葫芦10手</t>
+  </si>
+  <si>
+    <t>♣️J</t>
+  </si>
+  <si>
+    <t>♣️Q</t>
+  </si>
+  <si>
+    <t>双数顺子5手</t>
+  </si>
+  <si>
+    <t>♣️K</t>
+  </si>
+  <si>
+    <t>♦️A</t>
+  </si>
+  <si>
+    <t>♦️2</t>
+  </si>
+  <si>
+    <t>♦️3</t>
+  </si>
+  <si>
+    <t>四条2手</t>
+  </si>
+  <si>
+    <t>♦️4</t>
+  </si>
+  <si>
+    <t>♦️5</t>
+  </si>
+  <si>
+    <t>4条3手</t>
+  </si>
+  <si>
+    <t>♦️6</t>
+  </si>
+  <si>
+    <t>顺子8手</t>
+  </si>
+  <si>
+    <t>♦️7</t>
+  </si>
+  <si>
+    <t>同花8手</t>
+  </si>
+  <si>
+    <t>♦️8</t>
+  </si>
+  <si>
+    <t>单数顺子8手</t>
+  </si>
+  <si>
+    <t>♦️9</t>
+  </si>
+  <si>
+    <t>♦️10</t>
+  </si>
+  <si>
+    <t>♦️J</t>
+  </si>
+  <si>
+    <t>我爱5条</t>
+  </si>
+  <si>
+    <t>5条3手</t>
+  </si>
+  <si>
+    <t>♦️Q</t>
+  </si>
+  <si>
+    <t>我爱同花顺</t>
+  </si>
+  <si>
+    <t>同花顺3手</t>
+  </si>
+  <si>
+    <t>♦️K</t>
+  </si>
+  <si>
+    <t>我爱皇同</t>
+  </si>
+  <si>
+    <t>皇同2手</t>
+  </si>
+  <si>
+    <t>我爱高牌</t>
+  </si>
+  <si>
+    <t>高牌3手</t>
+  </si>
+  <si>
+    <t>一对10手</t>
   </si>
 </sst>
 </file>
@@ -229,6 +567,20 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.25"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="6" tint="-0.5"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -237,20 +589,6 @@
     <font>
       <sz val="11"/>
       <color theme="9" tint="-0.5"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="5" tint="-0.25"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -400,12 +738,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -726,7 +1070,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -750,16 +1094,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -768,117 +1112,135 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1406,564 +1768,783 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B3:M45"/>
+  <dimension ref="A3:L62"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
   <cols>
     <col min="2" max="2" width="16.3461538461538" customWidth="1"/>
     <col min="3" max="4" width="12.9807692307692" customWidth="1"/>
     <col min="5" max="5" width="12.4903846153846" customWidth="1"/>
     <col min="6" max="6" width="19.3846153846154" customWidth="1"/>
-    <col min="7" max="7" width="20.6730769230769" customWidth="1"/>
-    <col min="8" max="8" width="18.5769230769231" customWidth="1"/>
-    <col min="13" max="13" width="16.0192307692308" customWidth="1"/>
+    <col min="7" max="7" width="26.5961538461538" customWidth="1"/>
+    <col min="12" max="12" width="16.0192307692308" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:13">
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" spans="1:12">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" spans="1:12">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" spans="1:12">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="G3" t="s">
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:12">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8">
         <v>5</v>
       </c>
-      <c r="M3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13">
-      <c r="B4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="5" t="s">
+      <c r="B8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" spans="1:12">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13">
-      <c r="B5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="M5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13">
-      <c r="B6" s="5" t="s">
+      <c r="G9" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" spans="1:12">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="G10" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" spans="1:12">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:12">
+      <c r="A12">
+        <v>5</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" s="5" customFormat="1" spans="1:12">
+      <c r="A13">
+        <v>5</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" s="5" customFormat="1" spans="1:12">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13">
-      <c r="B7" s="5" t="s">
+      <c r="G14" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" s="7" customFormat="1" spans="1:12">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="G15" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" s="7" customFormat="1" spans="1:12">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="M7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13">
-      <c r="B8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" customFormat="1" spans="2:13">
-      <c r="B9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10" customFormat="1" spans="2:13">
-      <c r="B10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" customFormat="1" spans="2:13">
-      <c r="B11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="6" t="s">
+      <c r="G16" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:7">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:7">
+      <c r="A18">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:7">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:7">
+      <c r="A20">
+        <v>5</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:7">
+      <c r="A21">
+        <v>5</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:7">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:7">
+      <c r="A23">
+        <v>5</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" customFormat="1" spans="2:13">
-      <c r="B12" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="2:13">
-      <c r="B13" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="2:13">
-      <c r="B14" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="2:13">
-      <c r="B15" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="2:13">
-      <c r="B16" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" spans="2:13">
-      <c r="B17" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" spans="2:13">
-      <c r="B18" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" s="3" customFormat="1" spans="2:13">
-      <c r="B19" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" s="3" customFormat="1" spans="2:13">
-      <c r="B20" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" s="3" customFormat="1" spans="2:13">
-      <c r="B21" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" s="3" customFormat="1" spans="2:13">
-      <c r="B22" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13">
-      <c r="B23" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="2:13">
-      <c r="B24" t="s">
-        <v>35</v>
-      </c>
-      <c r="M24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13">
-      <c r="B25" t="s">
+      <c r="G23" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:7">
+      <c r="A24">
+        <v>5</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:7">
+      <c r="A25">
+        <v>5</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="26" spans="2:13">
-      <c r="B26" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="2:13">
-      <c r="B27" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28" spans="2:13">
-      <c r="B28" t="s">
+      <c r="G25" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:7">
+      <c r="A26">
+        <v>5</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="29" s="4" customFormat="1" spans="2:13">
-      <c r="B29" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F29" s="4" t="s">
+      <c r="G26" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:7">
+      <c r="A27">
+        <v>5</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:7">
+      <c r="A28">
+        <v>5</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:7">
+      <c r="A29">
+        <v>5</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="G29" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M29" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="30" s="4" customFormat="1" spans="2:13">
-      <c r="B30" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="31" spans="2:13">
-      <c r="B31" t="s">
-        <v>45</v>
-      </c>
-      <c r="F31" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="2:13">
-      <c r="B32" t="s">
-        <v>47</v>
-      </c>
-      <c r="F32" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6">
-      <c r="B34" t="s">
+      <c r="G29" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F34" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" t="s">
-        <v>51</v>
-      </c>
-      <c r="F35" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6">
-      <c r="B36" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6">
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:7">
+      <c r="A30"/>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:7">
+      <c r="A31"/>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:7">
+      <c r="A32"/>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:12">
+      <c r="A33"/>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:12">
+      <c r="A34"/>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:12">
+      <c r="A35"/>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:12">
+      <c r="A36"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:12">
+      <c r="A37"/>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:12">
+      <c r="A38"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:12">
+      <c r="A39"/>
+    </row>
+    <row r="40" spans="1:12">
       <c r="B40" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="41" spans="2:6">
+      <c r="E40" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
       <c r="B41" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="44" spans="2:6">
+      <c r="L41" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="B43" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
       <c r="B44" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="B45" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="46" s="15" customFormat="1" spans="1:12">
+      <c r="B46" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G46" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L46" s="15" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="2:6">
-      <c r="B45" t="s">
-        <v>59</v>
+    <row r="47" s="15" customFormat="1" spans="1:12">
+      <c r="B47" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G47" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L47" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="B48" t="s">
+        <v>67</v>
+      </c>
+      <c r="F48" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" t="s">
+        <v>68</v>
+      </c>
+      <c r="F49" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" t="s">
+        <v>70</v>
+      </c>
+      <c r="F51" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" t="s">
+        <v>71</v>
+      </c>
+      <c r="F52" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6">
+      <c r="B54" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6">
+      <c r="B57" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -1971,4 +2552,3398 @@
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A2:I82"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="2" max="2" width="12.3365384615385" customWidth="1"/>
+    <col min="3" max="3" width="12.8076923076923" customWidth="1"/>
+    <col min="4" max="4" width="13.7788461538462" customWidth="1"/>
+    <col min="6" max="6" width="13.7788461538462" customWidth="1"/>
+    <col min="7" max="7" width="18.1057692307692" customWidth="1"/>
+    <col min="8" max="8" width="17.625" customWidth="1"/>
+    <col min="9" max="9" width="17.9423076923077" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:9">
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" s="10" customFormat="1" spans="3:9">
+      <c r="C3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" s="10" customFormat="1" spans="3:9">
+      <c r="C4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" s="10" customFormat="1" spans="3:9">
+      <c r="C5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" s="10" customFormat="1" spans="3:9">
+      <c r="C6" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" s="10" customFormat="1" spans="3:9">
+      <c r="C7" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" s="10" customFormat="1" spans="3:9">
+      <c r="C8" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" s="10" customFormat="1" spans="3:9">
+      <c r="C9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" s="10" customFormat="1" spans="3:9">
+      <c r="C10" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" s="10" customFormat="1" spans="3:9">
+      <c r="C11" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" s="10" customFormat="1" spans="3:9">
+      <c r="C12" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" s="10" customFormat="1" spans="3:9">
+      <c r="C13" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" s="10" customFormat="1" spans="3:9">
+      <c r="C14" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" s="10" customFormat="1" spans="3:9">
+      <c r="C15" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="16" s="10" customFormat="1" spans="3:9">
+      <c r="C16" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" s="10" customFormat="1" spans="1:9">
+      <c r="C17" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" s="10" customFormat="1" spans="1:9">
+      <c r="C18" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" s="10" customFormat="1" spans="1:9">
+      <c r="C19" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="20" s="10" customFormat="1" spans="1:9">
+      <c r="C20" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H20" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" s="10" customFormat="1" spans="1:9">
+      <c r="C21" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" s="10" customFormat="1" spans="1:9">
+      <c r="C22" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H22" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" s="10" customFormat="1" spans="1:9">
+      <c r="C23" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" s="10" customFormat="1" spans="1:9">
+      <c r="C24" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="25" s="10" customFormat="1" spans="1:9">
+      <c r="C25" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" s="10" customFormat="1" spans="1:9">
+      <c r="C26" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" s="10" customFormat="1" spans="1:9">
+      <c r="C27" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" s="10" customFormat="1" spans="1:9">
+      <c r="C28" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="C30" t="s">
+        <v>1</v>
+      </c>
+      <c r="D30" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>80</v>
+      </c>
+      <c r="F30" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" t="s">
+        <v>5</v>
+      </c>
+      <c r="H30" t="s">
+        <v>6</v>
+      </c>
+      <c r="I30" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31">
+        <v>1</v>
+      </c>
+      <c r="B31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="2">
+        <v>0</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="2">
+        <v>0</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35">
+        <v>5</v>
+      </c>
+      <c r="B35" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="2">
+        <v>0</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36">
+        <v>6</v>
+      </c>
+      <c r="B36" t="s">
+        <v>90</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37">
+        <v>7</v>
+      </c>
+      <c r="B37" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38">
+        <v>8</v>
+      </c>
+      <c r="B38" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39">
+        <v>9</v>
+      </c>
+      <c r="B39" t="s">
+        <v>96</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40">
+        <v>10</v>
+      </c>
+      <c r="B40" t="s">
+        <v>98</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
+        <v>99</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H41" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42">
+        <v>12</v>
+      </c>
+      <c r="B42" t="s">
+        <v>101</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43">
+        <v>13</v>
+      </c>
+      <c r="B43" t="s">
+        <v>103</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44">
+        <v>14</v>
+      </c>
+      <c r="B44" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46">
+        <v>16</v>
+      </c>
+      <c r="B46" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47">
+        <v>17</v>
+      </c>
+      <c r="B47" t="s">
+        <v>110</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48">
+        <v>18</v>
+      </c>
+      <c r="B48" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49">
+        <v>19</v>
+      </c>
+      <c r="B49" t="s">
+        <v>114</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H49" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I49" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50">
+        <v>20</v>
+      </c>
+      <c r="B50" t="s">
+        <v>116</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51">
+        <v>21</v>
+      </c>
+      <c r="B51" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52">
+        <v>22</v>
+      </c>
+      <c r="B52" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53">
+        <v>23</v>
+      </c>
+      <c r="B53" t="s">
+        <v>121</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54">
+        <v>24</v>
+      </c>
+      <c r="B54" t="s">
+        <v>122</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55">
+        <v>25</v>
+      </c>
+      <c r="B55" t="s">
+        <v>123</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56">
+        <v>26</v>
+      </c>
+      <c r="B56" t="s">
+        <v>124</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57">
+        <v>27</v>
+      </c>
+      <c r="B57" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H57" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58">
+        <v>28</v>
+      </c>
+      <c r="B58" t="s">
+        <v>128</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H58" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59">
+        <v>29</v>
+      </c>
+      <c r="B59" t="s">
+        <v>129</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60">
+        <v>30</v>
+      </c>
+      <c r="B60" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61">
+        <v>31</v>
+      </c>
+      <c r="B61" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62">
+        <v>32</v>
+      </c>
+      <c r="B62" t="s">
+        <v>133</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63">
+        <v>33</v>
+      </c>
+      <c r="B63" t="s">
+        <v>134</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64">
+        <v>34</v>
+      </c>
+      <c r="B64" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65">
+        <v>35</v>
+      </c>
+      <c r="B65" t="s">
+        <v>138</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I65" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66">
+        <v>36</v>
+      </c>
+      <c r="B66" t="s">
+        <v>139</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67">
+        <v>37</v>
+      </c>
+      <c r="B67" t="s">
+        <v>141</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E67" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68">
+        <v>38</v>
+      </c>
+      <c r="B68" t="s">
+        <v>142</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69">
+        <v>39</v>
+      </c>
+      <c r="B69" t="s">
+        <v>144</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70">
+        <v>40</v>
+      </c>
+      <c r="B70" t="s">
+        <v>145</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="H70" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I70" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71">
+        <v>41</v>
+      </c>
+      <c r="B71" t="s">
+        <v>146</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72">
+        <v>42</v>
+      </c>
+      <c r="B72" t="s">
+        <v>147</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73">
+        <v>43</v>
+      </c>
+      <c r="B73" t="s">
+        <v>149</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74">
+        <v>44</v>
+      </c>
+      <c r="B74" t="s">
+        <v>150</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75">
+        <v>45</v>
+      </c>
+      <c r="B75" t="s">
+        <v>152</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I75" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76">
+        <v>46</v>
+      </c>
+      <c r="B76" t="s">
+        <v>154</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77">
+        <v>47</v>
+      </c>
+      <c r="B77" t="s">
+        <v>156</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I77" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78">
+        <v>48</v>
+      </c>
+      <c r="B78" t="s">
+        <v>158</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79">
+        <v>49</v>
+      </c>
+      <c r="B79" t="s">
+        <v>159</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E79" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="H79" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I79" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80">
+        <v>50</v>
+      </c>
+      <c r="B80" t="s">
+        <v>160</v>
+      </c>
+      <c r="C80" t="s">
+        <v>161</v>
+      </c>
+      <c r="D80" t="s">
+        <v>10</v>
+      </c>
+      <c r="E80" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="F80" t="s">
+        <v>22</v>
+      </c>
+      <c r="G80" t="s">
+        <v>162</v>
+      </c>
+      <c r="H80" t="s">
+        <v>50</v>
+      </c>
+      <c r="I80" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81">
+        <v>51</v>
+      </c>
+      <c r="B81" t="s">
+        <v>163</v>
+      </c>
+      <c r="C81" t="s">
+        <v>164</v>
+      </c>
+      <c r="D81" t="s">
+        <v>10</v>
+      </c>
+      <c r="E81" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="F81" t="s">
+        <v>22</v>
+      </c>
+      <c r="G81" t="s">
+        <v>165</v>
+      </c>
+      <c r="H81" t="s">
+        <v>50</v>
+      </c>
+      <c r="I81" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82">
+        <v>52</v>
+      </c>
+      <c r="B82" t="s">
+        <v>166</v>
+      </c>
+      <c r="C82" t="s">
+        <v>167</v>
+      </c>
+      <c r="D82" t="s">
+        <v>10</v>
+      </c>
+      <c r="E82" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="F82" t="s">
+        <v>22</v>
+      </c>
+      <c r="G82" t="s">
+        <v>168</v>
+      </c>
+      <c r="H82" t="s">
+        <v>50</v>
+      </c>
+      <c r="I82" t="s">
+        <v>167</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="B3:I55"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="4" max="4" width="13.7788461538462" customWidth="1"/>
+    <col min="5" max="5" width="13.1346153846154" customWidth="1"/>
+    <col min="6" max="6" width="8.48076923076923" customWidth="1"/>
+    <col min="8" max="8" width="15.5384615384615" customWidth="1"/>
+    <col min="9" max="9" width="16.8173076923077" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:9">
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="2:9">
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9">
+      <c r="B12">
+        <v>9</v>
+      </c>
+      <c r="C12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13">
+        <v>10</v>
+      </c>
+      <c r="C13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9">
+      <c r="B14">
+        <v>11</v>
+      </c>
+      <c r="C14" t="s">
+        <v>99</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0.08</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9">
+      <c r="B15">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9">
+      <c r="B16">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17">
+        <v>14</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F17" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18">
+        <v>15</v>
+      </c>
+      <c r="C18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F19" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21">
+        <v>18</v>
+      </c>
+      <c r="C21" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>114</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23">
+        <v>20</v>
+      </c>
+      <c r="C23" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24">
+        <v>21</v>
+      </c>
+      <c r="C24" t="s">
+        <v>117</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F24" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26">
+        <v>23</v>
+      </c>
+      <c r="C26" t="s">
+        <v>121</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F26" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9">
+      <c r="B27">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>122</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F27" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9">
+      <c r="B28">
+        <v>25</v>
+      </c>
+      <c r="C28" t="s">
+        <v>123</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F28" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9">
+      <c r="B29">
+        <v>26</v>
+      </c>
+      <c r="C29" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F29" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9">
+      <c r="B30">
+        <v>27</v>
+      </c>
+      <c r="C30" t="s">
+        <v>127</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F30" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9">
+      <c r="B31">
+        <v>28</v>
+      </c>
+      <c r="C31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9">
+      <c r="B32">
+        <v>29</v>
+      </c>
+      <c r="C32" t="s">
+        <v>129</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F32" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9">
+      <c r="B33">
+        <v>30</v>
+      </c>
+      <c r="C33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9">
+      <c r="B34">
+        <v>31</v>
+      </c>
+      <c r="C34" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F34" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9">
+      <c r="B35">
+        <v>32</v>
+      </c>
+      <c r="C35" t="s">
+        <v>133</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F35" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9">
+      <c r="B36">
+        <v>33</v>
+      </c>
+      <c r="C36" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F36" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9">
+      <c r="B37">
+        <v>34</v>
+      </c>
+      <c r="C37" t="s">
+        <v>136</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F37" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9">
+      <c r="B38">
+        <v>35</v>
+      </c>
+      <c r="C38" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9">
+      <c r="B39">
+        <v>36</v>
+      </c>
+      <c r="C39" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9">
+      <c r="B40">
+        <v>37</v>
+      </c>
+      <c r="C40" t="s">
+        <v>141</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9">
+      <c r="B41">
+        <v>38</v>
+      </c>
+      <c r="C41" t="s">
+        <v>142</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9">
+      <c r="B42">
+        <v>39</v>
+      </c>
+      <c r="C42" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9">
+      <c r="B43">
+        <v>40</v>
+      </c>
+      <c r="C43" t="s">
+        <v>145</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9">
+      <c r="B44">
+        <v>41</v>
+      </c>
+      <c r="C44" t="s">
+        <v>146</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F44" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9">
+      <c r="B45">
+        <v>42</v>
+      </c>
+      <c r="C45" t="s">
+        <v>147</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9">
+      <c r="B46">
+        <v>43</v>
+      </c>
+      <c r="C46" t="s">
+        <v>149</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9">
+      <c r="B47">
+        <v>44</v>
+      </c>
+      <c r="C47" t="s">
+        <v>150</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F47" s="4">
+        <v>0.08</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9">
+      <c r="B48">
+        <v>45</v>
+      </c>
+      <c r="C48" t="s">
+        <v>152</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9">
+      <c r="B49">
+        <v>46</v>
+      </c>
+      <c r="C49" t="s">
+        <v>154</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9">
+      <c r="B50">
+        <v>47</v>
+      </c>
+      <c r="C50" t="s">
+        <v>156</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9">
+      <c r="B51">
+        <v>48</v>
+      </c>
+      <c r="C51" t="s">
+        <v>158</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9">
+      <c r="B52">
+        <v>49</v>
+      </c>
+      <c r="C52" t="s">
+        <v>159</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H52" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="I52" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9">
+      <c r="B53">
+        <v>50</v>
+      </c>
+      <c r="C53" t="s">
+        <v>160</v>
+      </c>
+      <c r="D53" t="s">
+        <v>161</v>
+      </c>
+      <c r="E53" t="s">
+        <v>10</v>
+      </c>
+      <c r="F53" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="G53" t="s">
+        <v>22</v>
+      </c>
+      <c r="H53" t="s">
+        <v>162</v>
+      </c>
+      <c r="I53" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9">
+      <c r="B54">
+        <v>51</v>
+      </c>
+      <c r="C54" t="s">
+        <v>163</v>
+      </c>
+      <c r="D54" t="s">
+        <v>164</v>
+      </c>
+      <c r="E54" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="G54" t="s">
+        <v>22</v>
+      </c>
+      <c r="H54" t="s">
+        <v>165</v>
+      </c>
+      <c r="I54" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9">
+      <c r="B55">
+        <v>52</v>
+      </c>
+      <c r="C55" t="s">
+        <v>166</v>
+      </c>
+      <c r="D55" t="s">
+        <v>167</v>
+      </c>
+      <c r="E55" t="s">
+        <v>10</v>
+      </c>
+      <c r="F55" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="G55" t="s">
+        <v>22</v>
+      </c>
+      <c r="H55" t="s">
+        <v>168</v>
+      </c>
+      <c r="I55" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>